--- a/artfynd/A 727-2025 artfynd.xlsx
+++ b/artfynd/A 727-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119591982</v>
+        <v>87311681</v>
       </c>
       <c r="B2" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Timmerberget, Nb</t>
+          <t>Kvavaträskheden, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>817440</v>
+        <v>817384</v>
       </c>
       <c r="R2" t="n">
-        <v>7313729</v>
+        <v>7313723</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2020-05-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2020-05-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,37 +757,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>Frédéric Forsmark</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sofia Hagsand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sofia Hagsand</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119694244</v>
+        <v>119591979</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>4404</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>817513</v>
+        <v>817091</v>
       </c>
       <c r="R3" t="n">
-        <v>7313779</v>
+        <v>7313522</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,12 +866,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -890,12 +885,7 @@
         <v>119785945</v>
       </c>
       <c r="B4" t="n">
-        <v>79527</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,6 +980,212 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>119591982</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Timmerberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>817440</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7313729</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nederluleå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>87311694</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kvavaträskheden, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>817276</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7313587</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nederluleå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-05-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-05-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sofia Hagsand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sofia Hagsand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 727-2025 artfynd.xlsx
+++ b/artfynd/A 727-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87311681</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591979</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119785945</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591982</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,8 +1211,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87311694</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>